--- a/Data IKPA KPPN/2025/IKPA_KPPN_JANUARI_2025.xlsx
+++ b/Data IKPA KPPN/2025/IKPA_KPPN_JANUARI_2025.xlsx
@@ -541,16 +541,16 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>BATURAJA</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -559,35 +559,29 @@
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
       </c>
-      <c r="N2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O2" t="n">
-        <v>100</v>
-      </c>
-      <c r="P2" t="n">
-        <v>0</v>
-      </c>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
       <c r="Q2" t="n">
         <v>0</v>
       </c>

--- a/Data IKPA KPPN/2025/IKPA_KPPN_JANUARI_2025.xlsx
+++ b/Data IKPA KPPN/2025/IKPA_KPPN_JANUARI_2025.xlsx
@@ -541,59 +541,63 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>109</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>BATURAJA</t>
         </is>
       </c>
       <c r="D2" t="n">
+        <v>100</v>
+      </c>
+      <c r="E2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F2" t="n">
+        <v>100</v>
+      </c>
+      <c r="G2" t="n">
+        <v>100</v>
+      </c>
+      <c r="H2" t="n">
+        <v>100</v>
+      </c>
+      <c r="I2" t="n">
+        <v>100</v>
+      </c>
+      <c r="J2" t="n">
+        <v>100</v>
+      </c>
+      <c r="K2" t="n">
+        <v>100</v>
+      </c>
+      <c r="L2" t="n">
+        <v>100</v>
+      </c>
+      <c r="M2" t="n">
+        <v>100</v>
+      </c>
+      <c r="N2" t="n">
+        <v>100</v>
+      </c>
+      <c r="O2" t="n">
+        <v>100</v>
+      </c>
+      <c r="P2" t="n">
         <v>0</v>
       </c>
-      <c r="E2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
           <t>JANUARI</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
+      <c r="S2" t="n">
+        <v>2025</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
